--- a/Result/profitability/3026.xlsx
+++ b/Result/profitability/3026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.79</v>
       </c>
       <c r="M2" t="n">
-        <v>1.67625</v>
+        <v>1.935</v>
       </c>
       <c r="N2" t="n">
-        <v>18.37</v>
+        <v>19.51</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.74</v>
       </c>
       <c r="M3" t="n">
-        <v>1.54375</v>
+        <v>1.85625</v>
       </c>
       <c r="N3" t="n">
-        <v>17.55375</v>
+        <v>18.93375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.93</v>
       </c>
       <c r="M4" t="n">
-        <v>1.48875</v>
+        <v>1.7625</v>
       </c>
       <c r="N4" t="n">
-        <v>17.37</v>
+        <v>18.2075</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2775</v>
+        <v>1.5875</v>
       </c>
       <c r="N5" t="n">
-        <v>16.6375</v>
+        <v>17.43375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.66</v>
       </c>
       <c r="M6" t="n">
-        <v>1.18625</v>
+        <v>1.45875</v>
       </c>
       <c r="N6" t="n">
-        <v>16.30125</v>
+        <v>17.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.86</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0825</v>
+        <v>1.3375</v>
       </c>
       <c r="N7" t="n">
-        <v>15.95375</v>
+        <v>17.02375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.87</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9625</v>
+        <v>1.08875</v>
       </c>
       <c r="N8" t="n">
-        <v>15.85625</v>
+        <v>16.09875</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4097</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3025</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1073</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="G75" t="n">
+        <v>627</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.29%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>136</v>
+      </c>
+      <c r="J75" t="n">
+        <v>762</v>
+      </c>
+      <c r="K75" t="n">
+        <v>642</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.06125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.715</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3531468531468533</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.940000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08003300330033003</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.784172661870504</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.370000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3215547703180213</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
